--- a/backend/data/financials_by_company/000635.SZ.xlsx
+++ b/backend/data/financials_by_company/000635.SZ.xlsx
@@ -692,634 +692,634 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-1577801.321583</v>
+        <v>-9758642.0525</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01591</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>-233549089.98</v>
+        <v>196817867.99</v>
       </c>
       <c r="E2" t="n">
-        <v>-99172801.75</v>
+        <v>-39034568.21</v>
       </c>
       <c r="F2" t="n">
-        <v>-99172801.75</v>
+        <v>-39034568.21</v>
       </c>
       <c r="G2" t="n">
-        <v>-502560250.5</v>
+        <v>4294957.73</v>
       </c>
       <c r="H2" t="n">
-        <v>165843613.04</v>
+        <v>116876370.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2102503127.3</v>
+        <v>2074291336.82</v>
       </c>
       <c r="J2" t="n">
-        <v>-332721891.73</v>
+        <v>157783299.78</v>
       </c>
       <c r="K2" t="n">
-        <v>-498565504.77</v>
+        <v>40906929.18</v>
       </c>
       <c r="L2" t="n">
-        <v>-12983512.6</v>
-      </c>
-      <c r="M2" t="n">
-        <v>12119549.5</v>
-      </c>
+        <v>10427327.35</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>116135.03</v>
+        <v>10591422.09</v>
       </c>
       <c r="O2" t="n">
-        <v>-404965250.071583</v>
+        <v>33570883.8875</v>
       </c>
       <c r="P2" t="n">
-        <v>-502560250.5</v>
+        <v>4294957.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>2233171970.11</v>
-      </c>
-      <c r="R2" t="n">
-        <v>314809.07</v>
-      </c>
+        <v>2254071236.67</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-498425377.39</v>
+        <v>12303474.67</v>
       </c>
       <c r="T2" t="n">
-        <v>304581970</v>
+        <v>429495773</v>
       </c>
       <c r="U2" t="n">
-        <v>304581970</v>
+        <v>429495773</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.65</v>
+        <v>0.01</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.65</v>
+        <v>0.01</v>
       </c>
       <c r="X2" t="n">
-        <v>-502560250.5</v>
+        <v>4294957.73</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-502560250.5</v>
+        <v>4294957.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>-502560250.5</v>
+        <v>4294957.73</v>
       </c>
       <c r="AB2" t="n">
-        <v>-502560250.5</v>
+        <v>4294957.73</v>
       </c>
       <c r="AC2" t="n">
-        <v>-8124803.77</v>
+        <v>6743496.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>-510685054.27</v>
+        <v>11038453.98</v>
       </c>
       <c r="AE2" t="n">
-        <v>-12259676.88</v>
+        <v>-1265020.69</v>
       </c>
       <c r="AF2" t="n">
-        <v>-99190351.75</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>653785.8199999999</v>
-      </c>
+        <v>-39034568.21</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>2157443.37</v>
+        <v>-3871994.69</v>
       </c>
       <c r="AI2" t="n">
-        <v>96379122.56</v>
+        <v>42906562.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-12983512.6</v>
+        <v>10427327.35</v>
       </c>
       <c r="AK2" t="n">
-        <v>980098.13</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>12119549.5</v>
-      </c>
+        <v>164094.74</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>116135.03</v>
+        <v>10591422.09</v>
       </c>
       <c r="AN2" t="n">
-        <v>-387056786.28</v>
+        <v>40906929.18</v>
       </c>
       <c r="AO2" t="n">
-        <v>130668842.81</v>
+        <v>179779899.85</v>
       </c>
       <c r="AP2" t="n">
-        <v>27973521.77</v>
+        <v>111689915.68</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5633085.94</v>
+        <v>3564342.39</v>
       </c>
       <c r="AR2" t="n">
-        <v>3815363.36</v>
+        <v>2275471.32</v>
       </c>
       <c r="AS2" t="n">
-        <v>1817722.58</v>
+        <v>1288871.07</v>
       </c>
       <c r="AT2" t="n">
-        <v>4982229.29</v>
+        <v>598200.6800000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>92436389.45</v>
+        <v>41543617.48</v>
       </c>
       <c r="AV2" t="n">
-        <v>1053398.87</v>
+        <v>11601026.24</v>
       </c>
       <c r="AW2" t="n">
-        <v>91382990.58</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>314809.07</v>
-      </c>
+        <v>29942591.24</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>-256387943.47</v>
+        <v>220686829.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2102503127.3</v>
+        <v>2074291336.82</v>
       </c>
       <c r="BA2" t="n">
-        <v>1846115183.83</v>
+        <v>2294978165.85</v>
       </c>
       <c r="BB2" t="n">
-        <v>1846115183.83</v>
+        <v>2294978165.85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>986843.52</v>
+        <v>-29744265.319855</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.160624</v>
       </c>
       <c r="D3" t="n">
-        <v>-493879681.19</v>
+        <v>12342360.8</v>
       </c>
       <c r="E3" t="n">
-        <v>3947374.08</v>
+        <v>-185179180.47</v>
       </c>
       <c r="F3" t="n">
-        <v>3947374.08</v>
+        <v>-185179180.47</v>
       </c>
       <c r="G3" t="n">
-        <v>-667768724.47</v>
+        <v>-388869180.67</v>
       </c>
       <c r="H3" t="n">
-        <v>118243273.8</v>
+        <v>118452031.51</v>
       </c>
       <c r="I3" t="n">
-        <v>2164029965.62</v>
+        <v>2014947570.82</v>
       </c>
       <c r="J3" t="n">
-        <v>-489932307.11</v>
+        <v>-172836819.67</v>
       </c>
       <c r="K3" t="n">
-        <v>-608175580.91</v>
+        <v>-291288851.18</v>
       </c>
       <c r="L3" t="n">
-        <v>2240799.69</v>
-      </c>
-      <c r="M3" t="n">
-        <v>440116.47</v>
-      </c>
+        <v>11650922.41</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>2801692.71</v>
+        <v>11810195.57</v>
       </c>
       <c r="O3" t="n">
-        <v>-670729255.03</v>
+        <v>-233434265.519855</v>
       </c>
       <c r="P3" t="n">
-        <v>-667768724.47</v>
+        <v>-388869180.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>2349576759.29</v>
+        <v>2166344513.51</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>-596095554.3200001</v>
+        <v>-464832054.13</v>
       </c>
       <c r="T3" t="n">
-        <v>304917226</v>
+        <v>303804047</v>
       </c>
       <c r="U3" t="n">
-        <v>304917226</v>
+        <v>303804047</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.19</v>
+        <v>-1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.19</v>
+        <v>-1.28</v>
       </c>
       <c r="X3" t="n">
-        <v>-667768724.47</v>
+        <v>-388869180.67</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-667768724.47</v>
+        <v>-388869180.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>-667768724.47</v>
+        <v>-388869180.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>-667768724.47</v>
+        <v>-388869180.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>59153027.09</v>
+        <v>-74414606.73999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>-608615697.38</v>
+        <v>-463283787.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>-12520143.06</v>
+        <v>1548266.72</v>
       </c>
       <c r="AF3" t="n">
-        <v>3947374.08</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-48436433.06</v>
-      </c>
+        <v>-185179180.47</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-22372.98</v>
+        <v>124874.78</v>
       </c>
       <c r="AI3" t="n">
-        <v>44511431.96</v>
+        <v>185054305.69</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2240799.69</v>
+        <v>11650922.41</v>
       </c>
       <c r="AK3" t="n">
-        <v>120776.55</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>440116.47</v>
-      </c>
+        <v>159273.16</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>2801692.71</v>
+        <v>11810195.57</v>
       </c>
       <c r="AN3" t="n">
-        <v>-602380730.99</v>
+        <v>-291288851.18</v>
       </c>
       <c r="AO3" t="n">
-        <v>185546793.67</v>
+        <v>151396942.69</v>
       </c>
       <c r="AP3" t="n">
-        <v>23201334.45</v>
+        <v>36499653.43</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5359412.11</v>
+        <v>3708199.96</v>
       </c>
       <c r="AR3" t="n">
-        <v>2016470.21</v>
+        <v>2010173.53</v>
       </c>
       <c r="AS3" t="n">
-        <v>3342941.9</v>
+        <v>1698026.43</v>
       </c>
       <c r="AT3" t="n">
-        <v>3638193.66</v>
+        <v>1897867.53</v>
       </c>
       <c r="AU3" t="n">
-        <v>30581771</v>
+        <v>46683134.13</v>
       </c>
       <c r="AV3" t="n">
-        <v>1817060.3</v>
+        <v>12011832.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>28764710.7</v>
+        <v>34671301.93</v>
       </c>
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>-416833937.32</v>
+        <v>-139891908.49</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2164029965.62</v>
+        <v>2014947570.82</v>
       </c>
       <c r="BA3" t="n">
-        <v>1747196028.3</v>
+        <v>1875055662.33</v>
       </c>
       <c r="BB3" t="n">
-        <v>1747196028.3</v>
+        <v>1875055662.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-29744265.319855</v>
+        <v>986843.52</v>
       </c>
       <c r="C4" t="n">
-        <v>0.160624</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>12342360.8</v>
+        <v>-493879681.19</v>
       </c>
       <c r="E4" t="n">
-        <v>-185179180.47</v>
+        <v>3947374.08</v>
       </c>
       <c r="F4" t="n">
-        <v>-185179180.47</v>
+        <v>3947374.08</v>
       </c>
       <c r="G4" t="n">
-        <v>-388869180.67</v>
+        <v>-667768724.47</v>
       </c>
       <c r="H4" t="n">
-        <v>118452031.51</v>
+        <v>118243273.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2014947570.82</v>
+        <v>2164029965.62</v>
       </c>
       <c r="J4" t="n">
-        <v>-172836819.67</v>
+        <v>-489932307.11</v>
       </c>
       <c r="K4" t="n">
-        <v>-291288851.18</v>
+        <v>-608175580.91</v>
       </c>
       <c r="L4" t="n">
-        <v>11650922.41</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>2240799.69</v>
+      </c>
+      <c r="M4" t="n">
+        <v>440116.47</v>
+      </c>
       <c r="N4" t="n">
-        <v>11810195.57</v>
+        <v>2801692.71</v>
       </c>
       <c r="O4" t="n">
-        <v>-233434265.519855</v>
+        <v>-670729255.03</v>
       </c>
       <c r="P4" t="n">
-        <v>-388869180.67</v>
+        <v>-667768724.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>2166344513.51</v>
+        <v>2349576759.29</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-464832054.13</v>
+        <v>-596095554.3200001</v>
       </c>
       <c r="T4" t="n">
-        <v>303804047</v>
+        <v>304917226</v>
       </c>
       <c r="U4" t="n">
-        <v>303804047</v>
+        <v>304917226</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.28</v>
+        <v>-2.19</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.28</v>
+        <v>-2.19</v>
       </c>
       <c r="X4" t="n">
-        <v>-388869180.67</v>
+        <v>-667768724.47</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-388869180.67</v>
+        <v>-667768724.47</v>
       </c>
       <c r="AA4" t="n">
-        <v>-388869180.67</v>
+        <v>-667768724.47</v>
       </c>
       <c r="AB4" t="n">
-        <v>-388869180.67</v>
+        <v>-667768724.47</v>
       </c>
       <c r="AC4" t="n">
-        <v>-74414606.73999999</v>
+        <v>59153027.09</v>
       </c>
       <c r="AD4" t="n">
-        <v>-463283787.41</v>
+        <v>-608615697.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>1548266.72</v>
+        <v>-12520143.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>-185179180.47</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+        <v>3947374.08</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-48436433.06</v>
+      </c>
       <c r="AH4" t="n">
-        <v>124874.78</v>
+        <v>-22372.98</v>
       </c>
       <c r="AI4" t="n">
-        <v>185054305.69</v>
+        <v>44511431.96</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11650922.41</v>
+        <v>2240799.69</v>
       </c>
       <c r="AK4" t="n">
-        <v>159273.16</v>
-      </c>
-      <c r="AL4" t="inlineStr"/>
+        <v>120776.55</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>440116.47</v>
+      </c>
       <c r="AM4" t="n">
-        <v>11810195.57</v>
+        <v>2801692.71</v>
       </c>
       <c r="AN4" t="n">
-        <v>-291288851.18</v>
+        <v>-602380730.99</v>
       </c>
       <c r="AO4" t="n">
-        <v>151396942.69</v>
+        <v>185546793.67</v>
       </c>
       <c r="AP4" t="n">
-        <v>36499653.43</v>
+        <v>23201334.45</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3708199.96</v>
+        <v>5359412.11</v>
       </c>
       <c r="AR4" t="n">
-        <v>2010173.53</v>
+        <v>2016470.21</v>
       </c>
       <c r="AS4" t="n">
-        <v>1698026.43</v>
+        <v>3342941.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>1897867.53</v>
+        <v>3638193.66</v>
       </c>
       <c r="AU4" t="n">
-        <v>46683134.13</v>
+        <v>30581771</v>
       </c>
       <c r="AV4" t="n">
-        <v>12011832.2</v>
+        <v>1817060.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>34671301.93</v>
+        <v>28764710.7</v>
       </c>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>-139891908.49</v>
+        <v>-416833937.32</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2014947570.82</v>
+        <v>2164029965.62</v>
       </c>
       <c r="BA4" t="n">
-        <v>1875055662.33</v>
+        <v>1747196028.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>1875055662.33</v>
+        <v>1747196028.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-9758642.0525</v>
+        <v>-1577801.321583</v>
       </c>
       <c r="C5" t="n">
-        <v>0.25</v>
+        <v>0.01591</v>
       </c>
       <c r="D5" t="n">
-        <v>196817867.99</v>
+        <v>-233549089.98</v>
       </c>
       <c r="E5" t="n">
-        <v>-39034568.21</v>
+        <v>-99172801.75</v>
       </c>
       <c r="F5" t="n">
-        <v>-39034568.21</v>
+        <v>-99172801.75</v>
       </c>
       <c r="G5" t="n">
-        <v>4294957.73</v>
+        <v>-502560250.5</v>
       </c>
       <c r="H5" t="n">
-        <v>116876370.6</v>
+        <v>165843613.04</v>
       </c>
       <c r="I5" t="n">
-        <v>2074291336.82</v>
+        <v>2102503127.3</v>
       </c>
       <c r="J5" t="n">
-        <v>157783299.78</v>
+        <v>-332721891.73</v>
       </c>
       <c r="K5" t="n">
-        <v>40906929.18</v>
+        <v>-498565504.77</v>
       </c>
       <c r="L5" t="n">
-        <v>10427327.35</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>-12983512.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12119549.5</v>
+      </c>
       <c r="N5" t="n">
-        <v>10591422.09</v>
+        <v>116135.03</v>
       </c>
       <c r="O5" t="n">
-        <v>33570883.8875</v>
+        <v>-404965250.071583</v>
       </c>
       <c r="P5" t="n">
-        <v>4294957.73</v>
+        <v>-502560250.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2254071236.67</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>2233171970.11</v>
+      </c>
+      <c r="R5" t="n">
+        <v>314809.07</v>
+      </c>
       <c r="S5" t="n">
-        <v>12303474.67</v>
+        <v>-498425377.39</v>
       </c>
       <c r="T5" t="n">
-        <v>429495773</v>
+        <v>304581970</v>
       </c>
       <c r="U5" t="n">
-        <v>429495773</v>
+        <v>304581970</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01</v>
+        <v>-1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01</v>
+        <v>-1.65</v>
       </c>
       <c r="X5" t="n">
-        <v>4294957.73</v>
+        <v>-502560250.5</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4294957.73</v>
+        <v>-502560250.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>4294957.73</v>
+        <v>-502560250.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>4294957.73</v>
+        <v>-502560250.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>6743496.25</v>
+        <v>-8124803.77</v>
       </c>
       <c r="AD5" t="n">
-        <v>11038453.98</v>
+        <v>-510685054.27</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1265020.69</v>
+        <v>-12259676.88</v>
       </c>
       <c r="AF5" t="n">
-        <v>-39034568.21</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>-99190351.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>653785.8199999999</v>
+      </c>
       <c r="AH5" t="n">
-        <v>-3871994.69</v>
+        <v>2157443.37</v>
       </c>
       <c r="AI5" t="n">
-        <v>42906562.9</v>
+        <v>96379122.56</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10427327.35</v>
+        <v>-12983512.6</v>
       </c>
       <c r="AK5" t="n">
-        <v>164094.74</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
+        <v>980098.13</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>12119549.5</v>
+      </c>
       <c r="AM5" t="n">
-        <v>10591422.09</v>
+        <v>116135.03</v>
       </c>
       <c r="AN5" t="n">
-        <v>40906929.18</v>
+        <v>-387056786.28</v>
       </c>
       <c r="AO5" t="n">
-        <v>179779899.85</v>
+        <v>130668842.81</v>
       </c>
       <c r="AP5" t="n">
-        <v>111689915.68</v>
+        <v>27973521.77</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3564342.39</v>
+        <v>5633085.94</v>
       </c>
       <c r="AR5" t="n">
-        <v>2275471.32</v>
+        <v>3815363.36</v>
       </c>
       <c r="AS5" t="n">
-        <v>1288871.07</v>
+        <v>1817722.58</v>
       </c>
       <c r="AT5" t="n">
-        <v>598200.6800000001</v>
+        <v>4982229.29</v>
       </c>
       <c r="AU5" t="n">
-        <v>41543617.48</v>
+        <v>92436389.45</v>
       </c>
       <c r="AV5" t="n">
-        <v>11601026.24</v>
+        <v>1053398.87</v>
       </c>
       <c r="AW5" t="n">
-        <v>29942591.24</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+        <v>91382990.58</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>314809.07</v>
+      </c>
       <c r="AY5" t="n">
-        <v>220686829.03</v>
+        <v>-256387943.47</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2074291336.82</v>
+        <v>2102503127.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>2294978165.85</v>
+        <v>1846115183.83</v>
       </c>
       <c r="BB5" t="n">
-        <v>2294978165.85</v>
+        <v>1846115183.83</v>
       </c>
     </row>
   </sheetData>
@@ -1650,724 +1650,724 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>303486737</v>
+        <v>303087602</v>
       </c>
       <c r="C2" t="n">
-        <v>303486737</v>
-      </c>
-      <c r="D2" t="n">
-        <v>638141513.7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>722727543.27</v>
-      </c>
+        <v>303087602</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>1033512388.01</v>
+        <v>2589003992.61</v>
       </c>
       <c r="G2" t="n">
-        <v>1757712839.97</v>
+        <v>2657801545.36</v>
       </c>
       <c r="H2" t="n">
-        <v>-1006497155.53</v>
+        <v>1173517112.27</v>
       </c>
       <c r="I2" t="n">
-        <v>1033512388.01</v>
+        <v>2589003992.61</v>
       </c>
       <c r="J2" t="n">
-        <v>1100116820.25</v>
+        <v>2657801545.36</v>
       </c>
       <c r="K2" t="n">
-        <v>1205116820.25</v>
+        <v>2657801545.36</v>
       </c>
       <c r="L2" t="n">
-        <v>1100116820.25</v>
+        <v>2657801545.36</v>
       </c>
       <c r="M2" t="n">
-        <v>1100116820.25</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2921668.2</v>
-      </c>
+        <v>2657801545.36</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>-1203922119.33</v>
+        <v>355276036.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1861929475.04</v>
+        <v>1878568841.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>303486737</v>
+        <v>303087602</v>
       </c>
       <c r="R2" t="n">
-        <v>303486737</v>
+        <v>303087602</v>
       </c>
       <c r="S2" t="n">
-        <v>1471921233.76</v>
+        <v>398042780.89</v>
       </c>
       <c r="T2" t="n">
-        <v>198929215.57</v>
-      </c>
-      <c r="U2" t="n">
-        <v>42985855.14</v>
-      </c>
+        <v>5074287.29</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>50943360.43</v>
-      </c>
-      <c r="W2" t="n">
-        <v>105000000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>105000000</v>
-      </c>
+        <v>5074287.29</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>1272992018.19</v>
+        <v>392968493.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>11345589.35</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>617727543.27</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>552596019.72</v>
-      </c>
+        <v>9807980.310000001</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>616595169.22</v>
+        <v>354622352.49</v>
       </c>
       <c r="AD2" t="n">
-        <v>88525069.83</v>
+        <v>62164784.61</v>
       </c>
       <c r="AE2" t="n">
-        <v>10032939.03</v>
+        <v>4387568.12</v>
       </c>
       <c r="AF2" t="n">
-        <v>518037160.36</v>
+        <v>288069999.76</v>
       </c>
       <c r="AG2" t="n">
-        <v>2572038054.01</v>
+        <v>3055844326.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2305543191.35</v>
+        <v>1489358720.38</v>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>53596685.36</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2301968.21</v>
-      </c>
+        <v>27704496.86</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>66604432.24</v>
+        <v>68797552.75</v>
       </c>
       <c r="AM2" t="n">
-        <v>66604432.24</v>
+        <v>68797552.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>2183040105.54</v>
+        <v>1392856670.77</v>
       </c>
       <c r="AO2" t="n">
-        <v>-3390501768.47</v>
+        <v>-3397908256.93</v>
       </c>
       <c r="AP2" t="n">
-        <v>5573541874.01</v>
+        <v>4790764927.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>148388378.6</v>
+        <v>13951737.36</v>
       </c>
       <c r="AR2" t="n">
-        <v>61159603.56</v>
+        <v>53698816.69</v>
       </c>
       <c r="AS2" t="n">
-        <v>3841700084.66</v>
+        <v>3398864363.52</v>
       </c>
       <c r="AT2" t="n">
-        <v>1522293807.19</v>
+        <v>1324250010.13</v>
       </c>
       <c r="AU2" t="n">
-        <v>266494862.66</v>
+        <v>1566485605.87</v>
       </c>
       <c r="AV2" t="n">
-        <v>8368759.4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>89005.5</v>
-      </c>
+        <v>19502631.28</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>6105880.42</v>
+        <v>5180321.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>123812608.27</v>
+        <v>141059297.82</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>58430709.06</v>
+        <v>59835783.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>1937441.99</v>
+        <v>4591495.52</v>
       </c>
       <c r="BC2" t="n">
-        <v>63444457.22</v>
+        <v>76632018.63</v>
       </c>
       <c r="BD2" t="n">
-        <v>73497914.41</v>
+        <v>800282132.63</v>
       </c>
       <c r="BE2" t="n">
-        <v>35166188.64</v>
+        <v>5382113.53</v>
       </c>
       <c r="BF2" t="n">
-        <v>-2273434.44</v>
+        <v>-502553.86</v>
       </c>
       <c r="BG2" t="n">
-        <v>37439623.08</v>
+        <v>5884667.39</v>
       </c>
       <c r="BH2" t="n">
-        <v>19454506.02</v>
+        <v>595079109.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>19454506.02</v>
+        <v>595079109.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>17504838.28</v>
+        <v>4373333.33</v>
       </c>
       <c r="BK2" t="n">
-        <v>1000</v>
+        <v>590705776.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>303915506</v>
+        <v>304610502</v>
       </c>
       <c r="C3" t="n">
-        <v>303915506</v>
-      </c>
-      <c r="D3" t="n">
-        <v>159502051.05</v>
-      </c>
+        <v>304610502</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>182734808.89</v>
+        <v>2607944.44</v>
       </c>
       <c r="F3" t="n">
-        <v>1535425089.29</v>
+        <v>2197438855.22</v>
       </c>
       <c r="G3" t="n">
-        <v>1783996592.37</v>
+        <v>2271722477.13</v>
       </c>
       <c r="H3" t="n">
-        <v>-418661980.38</v>
+        <v>585779542.08</v>
       </c>
       <c r="I3" t="n">
-        <v>1535425089.29</v>
+        <v>2197438855.22</v>
       </c>
       <c r="J3" t="n">
-        <v>1601396592.37</v>
+        <v>2269122477.13</v>
       </c>
       <c r="K3" t="n">
-        <v>1783996592.37</v>
+        <v>2271722477.13</v>
       </c>
       <c r="L3" t="n">
-        <v>1601396592.37</v>
+        <v>2269122477.13</v>
       </c>
       <c r="M3" t="n">
-        <v>1601396592.37</v>
+        <v>2269122477.13</v>
       </c>
       <c r="N3" t="n">
-        <v>6060257.28</v>
+        <v>11147628</v>
       </c>
       <c r="O3" t="n">
-        <v>-701361868.83</v>
+        <v>-33593144.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1864252134.17</v>
+        <v>1868644508.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>303915506</v>
+        <v>304610502</v>
       </c>
       <c r="R3" t="n">
-        <v>303915506</v>
+        <v>304610502</v>
       </c>
       <c r="S3" t="n">
-        <v>1080066988.1</v>
+        <v>462248218.34</v>
       </c>
       <c r="T3" t="n">
-        <v>288734701.4</v>
+        <v>34401262.99</v>
       </c>
       <c r="U3" t="n">
-        <v>52883642.81</v>
+        <v>11247139.75</v>
       </c>
       <c r="V3" t="n">
-        <v>53251058.59</v>
+        <v>20554123.24</v>
       </c>
       <c r="W3" t="n">
-        <v>182600000</v>
+        <v>2600000</v>
       </c>
       <c r="X3" t="n">
-        <v>182600000</v>
+        <v>2600000</v>
       </c>
       <c r="Y3" t="n">
-        <v>791332286.7</v>
+        <v>427846955.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>13363287.85</v>
+        <v>10981693.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>134808.89</v>
+        <v>7944.44</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>752272313.6</v>
+        <v>389368164.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>90848319.15000001</v>
+        <v>64627512.03</v>
       </c>
       <c r="AE3" t="n">
-        <v>9181744.449999999</v>
+        <v>8987787.76</v>
       </c>
       <c r="AF3" t="n">
-        <v>652242250</v>
+        <v>315752864.86</v>
       </c>
       <c r="AG3" t="n">
-        <v>2681463580.47</v>
+        <v>2731370695.47</v>
       </c>
       <c r="AH3" t="n">
-        <v>2308793274.15</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>1717744198.04</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>29308509.83</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>45471881.58</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2615761.81</v>
-      </c>
+        <v>104624908.67</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>65971503.08</v>
+        <v>71683621.91</v>
       </c>
       <c r="AM3" t="n">
-        <v>65971503.08</v>
+        <v>71683621.91</v>
       </c>
       <c r="AN3" t="n">
-        <v>2194734127.68</v>
+        <v>1512127157.63</v>
       </c>
       <c r="AO3" t="n">
-        <v>-3209670337.29</v>
+        <v>-3481724938.01</v>
       </c>
       <c r="AP3" t="n">
-        <v>5404404464.97</v>
+        <v>4993852095.64</v>
       </c>
       <c r="AQ3" t="n">
-        <v>835593696.39</v>
+        <v>188642644.13</v>
       </c>
       <c r="AR3" t="n">
-        <v>53061906.75</v>
+        <v>53353421.31</v>
       </c>
       <c r="AS3" t="n">
-        <v>3247040430.29</v>
+        <v>3421959442.32</v>
       </c>
       <c r="AT3" t="n">
-        <v>1268708431.54</v>
+        <v>1329896587.88</v>
       </c>
       <c r="AU3" t="n">
-        <v>372670306.32</v>
+        <v>1013626497.43</v>
       </c>
       <c r="AV3" t="n">
-        <v>11965730.1</v>
+        <v>11255949.72</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>24555571.87</v>
+        <v>3660138.13</v>
       </c>
       <c r="AY3" t="n">
-        <v>150889196.86</v>
+        <v>294227394.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>69388675.78</v>
+        <v>228097019.95</v>
       </c>
       <c r="BB3" t="n">
-        <v>1496466.77</v>
+        <v>1856415.89</v>
       </c>
       <c r="BC3" t="n">
-        <v>80004054.31</v>
+        <v>64273958.56</v>
       </c>
       <c r="BD3" t="n">
-        <v>148890039.58</v>
+        <v>260533285.89</v>
       </c>
       <c r="BE3" t="n">
-        <v>13271818.96</v>
+        <v>2538424.99</v>
       </c>
       <c r="BF3" t="n">
-        <v>-105205.1</v>
+        <v>-581078.26</v>
       </c>
       <c r="BG3" t="n">
-        <v>13377024.06</v>
+        <v>3119503.25</v>
       </c>
       <c r="BH3" t="n">
-        <v>23097948.95</v>
+        <v>441411304.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>23097948.95</v>
+        <v>441411304.3</v>
       </c>
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>23077689.78</v>
+        <v>441411304.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>304610502</v>
+        <v>303915506</v>
       </c>
       <c r="C4" t="n">
-        <v>304610502</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>303915506</v>
+      </c>
+      <c r="D4" t="n">
+        <v>159502051.05</v>
+      </c>
       <c r="E4" t="n">
-        <v>2607944.44</v>
+        <v>182734808.89</v>
       </c>
       <c r="F4" t="n">
-        <v>2197438855.22</v>
+        <v>1535425089.29</v>
       </c>
       <c r="G4" t="n">
-        <v>2271722477.13</v>
+        <v>1783996592.37</v>
       </c>
       <c r="H4" t="n">
-        <v>585779542.08</v>
+        <v>-418661980.38</v>
       </c>
       <c r="I4" t="n">
-        <v>2197438855.22</v>
+        <v>1535425089.29</v>
       </c>
       <c r="J4" t="n">
-        <v>2269122477.13</v>
+        <v>1601396592.37</v>
       </c>
       <c r="K4" t="n">
-        <v>2271722477.13</v>
+        <v>1783996592.37</v>
       </c>
       <c r="L4" t="n">
-        <v>2269122477.13</v>
+        <v>1601396592.37</v>
       </c>
       <c r="M4" t="n">
-        <v>2269122477.13</v>
+        <v>1601396592.37</v>
       </c>
       <c r="N4" t="n">
-        <v>11147628</v>
+        <v>6060257.28</v>
       </c>
       <c r="O4" t="n">
-        <v>-33593144.36</v>
+        <v>-701361868.83</v>
       </c>
       <c r="P4" t="n">
-        <v>1868644508.89</v>
+        <v>1864252134.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>304610502</v>
+        <v>303915506</v>
       </c>
       <c r="R4" t="n">
-        <v>304610502</v>
+        <v>303915506</v>
       </c>
       <c r="S4" t="n">
-        <v>462248218.34</v>
+        <v>1080066988.1</v>
       </c>
       <c r="T4" t="n">
-        <v>34401262.99</v>
+        <v>288734701.4</v>
       </c>
       <c r="U4" t="n">
-        <v>11247139.75</v>
+        <v>52883642.81</v>
       </c>
       <c r="V4" t="n">
-        <v>20554123.24</v>
+        <v>53251058.59</v>
       </c>
       <c r="W4" t="n">
-        <v>2600000</v>
+        <v>182600000</v>
       </c>
       <c r="X4" t="n">
-        <v>2600000</v>
+        <v>182600000</v>
       </c>
       <c r="Y4" t="n">
-        <v>427846955.35</v>
+        <v>791332286.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>10981693.83</v>
+        <v>13363287.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>7944.44</v>
+        <v>134808.89</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>389368164.65</v>
+        <v>752272313.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>64627512.03</v>
+        <v>90848319.15000001</v>
       </c>
       <c r="AE4" t="n">
-        <v>8987787.76</v>
+        <v>9181744.449999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>315752864.86</v>
+        <v>652242250</v>
       </c>
       <c r="AG4" t="n">
-        <v>2731370695.47</v>
+        <v>2681463580.47</v>
       </c>
       <c r="AH4" t="n">
-        <v>1717744198.04</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>29308509.83</v>
-      </c>
+        <v>2308793274.15</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>104624908.67</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
+        <v>45471881.58</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2615761.81</v>
+      </c>
       <c r="AL4" t="n">
-        <v>71683621.91</v>
+        <v>65971503.08</v>
       </c>
       <c r="AM4" t="n">
-        <v>71683621.91</v>
+        <v>65971503.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>1512127157.63</v>
+        <v>2194734127.68</v>
       </c>
       <c r="AO4" t="n">
-        <v>-3481724938.01</v>
+        <v>-3209670337.29</v>
       </c>
       <c r="AP4" t="n">
-        <v>4993852095.64</v>
+        <v>5404404464.97</v>
       </c>
       <c r="AQ4" t="n">
-        <v>188642644.13</v>
+        <v>835593696.39</v>
       </c>
       <c r="AR4" t="n">
-        <v>53353421.31</v>
+        <v>53061906.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>3421959442.32</v>
+        <v>3247040430.29</v>
       </c>
       <c r="AT4" t="n">
-        <v>1329896587.88</v>
+        <v>1268708431.54</v>
       </c>
       <c r="AU4" t="n">
-        <v>1013626497.43</v>
+        <v>372670306.32</v>
       </c>
       <c r="AV4" t="n">
-        <v>11255949.72</v>
+        <v>11965730.1</v>
       </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>3660138.13</v>
+        <v>24555571.87</v>
       </c>
       <c r="AY4" t="n">
-        <v>294227394.4</v>
+        <v>150889196.86</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>228097019.95</v>
+        <v>69388675.78</v>
       </c>
       <c r="BB4" t="n">
-        <v>1856415.89</v>
+        <v>1496466.77</v>
       </c>
       <c r="BC4" t="n">
-        <v>64273958.56</v>
+        <v>80004054.31</v>
       </c>
       <c r="BD4" t="n">
-        <v>260533285.89</v>
+        <v>148890039.58</v>
       </c>
       <c r="BE4" t="n">
-        <v>2538424.99</v>
+        <v>13271818.96</v>
       </c>
       <c r="BF4" t="n">
-        <v>-581078.26</v>
+        <v>-105205.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>3119503.25</v>
+        <v>13377024.06</v>
       </c>
       <c r="BH4" t="n">
-        <v>441411304.3</v>
+        <v>23097948.95</v>
       </c>
       <c r="BI4" t="n">
-        <v>441411304.3</v>
+        <v>23097948.95</v>
       </c>
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="n">
-        <v>441411304.3</v>
+        <v>23077689.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>303087602</v>
+        <v>303486737</v>
       </c>
       <c r="C5" t="n">
-        <v>303087602</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+        <v>303486737</v>
+      </c>
+      <c r="D5" t="n">
+        <v>638141513.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>722727543.27</v>
+      </c>
       <c r="F5" t="n">
-        <v>2589003992.61</v>
+        <v>1033512388.01</v>
       </c>
       <c r="G5" t="n">
-        <v>2657801545.36</v>
+        <v>1757712839.97</v>
       </c>
       <c r="H5" t="n">
-        <v>1173517112.27</v>
+        <v>-1006497155.53</v>
       </c>
       <c r="I5" t="n">
-        <v>2589003992.61</v>
+        <v>1033512388.01</v>
       </c>
       <c r="J5" t="n">
-        <v>2657801545.36</v>
+        <v>1100116820.25</v>
       </c>
       <c r="K5" t="n">
-        <v>2657801545.36</v>
+        <v>1205116820.25</v>
       </c>
       <c r="L5" t="n">
-        <v>2657801545.36</v>
+        <v>1100116820.25</v>
       </c>
       <c r="M5" t="n">
-        <v>2657801545.36</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>1100116820.25</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2921668.2</v>
+      </c>
       <c r="O5" t="n">
-        <v>355276036.31</v>
+        <v>-1203922119.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1878568841.02</v>
+        <v>1861929475.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>303087602</v>
+        <v>303486737</v>
       </c>
       <c r="R5" t="n">
-        <v>303087602</v>
+        <v>303486737</v>
       </c>
       <c r="S5" t="n">
-        <v>398042780.89</v>
+        <v>1471921233.76</v>
       </c>
       <c r="T5" t="n">
-        <v>5074287.29</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>198929215.57</v>
+      </c>
+      <c r="U5" t="n">
+        <v>42985855.14</v>
+      </c>
       <c r="V5" t="n">
-        <v>5074287.29</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+        <v>50943360.43</v>
+      </c>
+      <c r="W5" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>105000000</v>
+      </c>
       <c r="Y5" t="n">
-        <v>392968493.6</v>
+        <v>1272992018.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>9807980.310000001</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+        <v>11345589.35</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>617727543.27</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>552596019.72</v>
+      </c>
       <c r="AC5" t="n">
-        <v>354622352.49</v>
+        <v>616595169.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>62164784.61</v>
+        <v>88525069.83</v>
       </c>
       <c r="AE5" t="n">
-        <v>4387568.12</v>
+        <v>10032939.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>288069999.76</v>
+        <v>518037160.36</v>
       </c>
       <c r="AG5" t="n">
-        <v>3055844326.25</v>
+        <v>2572038054.01</v>
       </c>
       <c r="AH5" t="n">
-        <v>1489358720.38</v>
+        <v>2305543191.35</v>
       </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>27704496.86</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>53596685.36</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2301968.21</v>
+      </c>
       <c r="AL5" t="n">
-        <v>68797552.75</v>
+        <v>66604432.24</v>
       </c>
       <c r="AM5" t="n">
-        <v>68797552.75</v>
+        <v>66604432.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>1392856670.77</v>
+        <v>2183040105.54</v>
       </c>
       <c r="AO5" t="n">
-        <v>-3397908256.93</v>
+        <v>-3390501768.47</v>
       </c>
       <c r="AP5" t="n">
-        <v>4790764927.7</v>
+        <v>5573541874.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13951737.36</v>
+        <v>148388378.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>53698816.69</v>
+        <v>61159603.56</v>
       </c>
       <c r="AS5" t="n">
-        <v>3398864363.52</v>
+        <v>3841700084.66</v>
       </c>
       <c r="AT5" t="n">
-        <v>1324250010.13</v>
+        <v>1522293807.19</v>
       </c>
       <c r="AU5" t="n">
-        <v>1566485605.87</v>
+        <v>266494862.66</v>
       </c>
       <c r="AV5" t="n">
-        <v>19502631.28</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+        <v>8368759.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>89005.5</v>
+      </c>
       <c r="AX5" t="n">
-        <v>5180321.01</v>
+        <v>6105880.42</v>
       </c>
       <c r="AY5" t="n">
-        <v>141059297.82</v>
+        <v>123812608.27</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>59835783.67</v>
+        <v>58430709.06</v>
       </c>
       <c r="BB5" t="n">
-        <v>4591495.52</v>
+        <v>1937441.99</v>
       </c>
       <c r="BC5" t="n">
-        <v>76632018.63</v>
+        <v>63444457.22</v>
       </c>
       <c r="BD5" t="n">
-        <v>800282132.63</v>
+        <v>73497914.41</v>
       </c>
       <c r="BE5" t="n">
-        <v>5382113.53</v>
+        <v>35166188.64</v>
       </c>
       <c r="BF5" t="n">
-        <v>-502553.86</v>
+        <v>-2273434.44</v>
       </c>
       <c r="BG5" t="n">
-        <v>5884667.39</v>
+        <v>37439623.08</v>
       </c>
       <c r="BH5" t="n">
-        <v>595079109.6</v>
+        <v>19454506.02</v>
       </c>
       <c r="BI5" t="n">
-        <v>595079109.6</v>
+        <v>19454506.02</v>
       </c>
       <c r="BJ5" t="n">
-        <v>4373333.33</v>
+        <v>17504838.28</v>
       </c>
       <c r="BK5" t="n">
-        <v>590705776.27</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -2603,504 +2603,504 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-531618207.94</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-230000000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>769574489.53</v>
-      </c>
+        <v>134544640.53</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-37800931.38</v>
+        <v>-12903370.69</v>
       </c>
       <c r="F2" t="n">
-        <v>17505838.28</v>
+        <v>40705776.27</v>
       </c>
       <c r="G2" t="n">
-        <v>23097948.95</v>
+        <v>129107915.6</v>
       </c>
       <c r="H2" t="n">
-        <v>-5592110.67</v>
+        <v>-88402139.33</v>
       </c>
       <c r="I2" t="n">
-        <v>525590847.27</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-2751428.13</v>
-      </c>
+        <v>-42432264.28</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>-11232214.13</v>
-      </c>
-      <c r="L2" t="n">
-        <v>539574489.53</v>
-      </c>
-      <c r="M2" t="n">
-        <v>539574489.53</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-230000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>769574489.53</v>
-      </c>
+        <v>-42432264.28</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-37365681.38</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+        <v>-193417886.27</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-194764999</v>
+      </c>
+      <c r="R2" t="n">
+        <v>455235001</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-650000000</v>
+      </c>
       <c r="T2" t="n">
-        <v>-37365681.38</v>
+        <v>1347112.73</v>
       </c>
       <c r="U2" t="n">
-        <v>435250</v>
+        <v>14250483.42</v>
       </c>
       <c r="V2" t="n">
-        <v>-37800931.38</v>
+        <v>-12903370.69</v>
       </c>
       <c r="W2" t="n">
-        <v>-493817276.56</v>
+        <v>147448011.22</v>
       </c>
       <c r="X2" t="n">
-        <v>-270879187.39</v>
+        <v>4305432.87</v>
       </c>
       <c r="Y2" t="n">
-        <v>-8124803.78</v>
+        <v>1703373.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>-158007027.69</v>
+        <v>-91990611.37</v>
       </c>
       <c r="AA2" t="n">
-        <v>-24898272.05</v>
+        <v>-45074276.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>-79849083.87</v>
+        <v>139666947.82</v>
       </c>
       <c r="AC2" t="n">
-        <v>12119549.5</v>
+        <v>-9589220.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>165843613.04</v>
+        <v>116876370.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>4800509.36</v>
+        <v>3031318.47</v>
       </c>
       <c r="AF2" t="n">
-        <v>161043103.68</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-805273.24</v>
-      </c>
+        <v>113845052.13</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>3927706.1</v>
+        <v>-7474097.45</v>
       </c>
       <c r="AI2" t="n">
-        <v>-502560250.5</v>
+        <v>4294957.73</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-493817276.56</v>
+        <v>147448011.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>-32319618.93</v>
+        <v>-136545917.81</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1463642099.72</v>
+        <v>-981942740.05</v>
       </c>
       <c r="AM2" t="n">
-        <v>-43235046.4</v>
+        <v>-26366028.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>-457751016.15</v>
+        <v>-351895863.3</v>
       </c>
       <c r="AO2" t="n">
-        <v>-962656037.17</v>
+        <v>-603680848.13</v>
       </c>
       <c r="AP2" t="n">
-        <v>1002144442.09</v>
+        <v>1265936669.08</v>
       </c>
       <c r="AQ2" t="n">
-        <v>38342746.31</v>
+        <v>28858886.66</v>
       </c>
       <c r="AR2" t="n">
-        <v>963801695.78</v>
+        <v>1237077782.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-674255284.55</v>
+        <v>-180496264.05</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>180000000</v>
+        <v>2600000</v>
       </c>
       <c r="E3" t="n">
-        <v>-77882054.08</v>
+        <v>-18912618.08</v>
       </c>
       <c r="F3" t="n">
-        <v>23097948.95</v>
+        <v>9796343.220000001</v>
       </c>
       <c r="G3" t="n">
-        <v>9796343.220000001</v>
+        <v>40705776.27</v>
       </c>
       <c r="H3" t="n">
-        <v>13301605.73</v>
+        <v>-30909433.05</v>
       </c>
       <c r="I3" t="n">
-        <v>174510990.28</v>
+        <v>13747628</v>
       </c>
       <c r="J3" t="n">
-        <v>-5100259.72</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-388750</v>
-      </c>
+        <v>11147628</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>180000000</v>
+        <v>2600000</v>
       </c>
       <c r="M3" t="n">
-        <v>180000000</v>
+        <v>2600000</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>180000000</v>
+        <v>2600000</v>
       </c>
       <c r="P3" t="n">
-        <v>435163845.92</v>
+        <v>116926584.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>433820500</v>
+        <v>133902000</v>
       </c>
       <c r="R3" t="n">
-        <v>513820500</v>
+        <v>1447902000</v>
       </c>
       <c r="S3" t="n">
-        <v>-80000000</v>
+        <v>-1314000000</v>
       </c>
       <c r="T3" t="n">
-        <v>1343345.92</v>
+        <v>-16975415.08</v>
       </c>
       <c r="U3" t="n">
-        <v>79225400</v>
+        <v>1937203</v>
       </c>
       <c r="V3" t="n">
-        <v>-77882054.08</v>
+        <v>-18912618.08</v>
       </c>
       <c r="W3" t="n">
-        <v>-596373230.47</v>
+        <v>-161583645.97</v>
       </c>
       <c r="X3" t="n">
-        <v>-40113299.04</v>
+        <v>-67144583.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>59153027.09</v>
+        <v>-76920411.81</v>
       </c>
       <c r="Z3" t="n">
-        <v>182225344.21</v>
+        <v>-201199512.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>98826765.58</v>
+        <v>-155895461.96</v>
       </c>
       <c r="AB3" t="n">
-        <v>-380318435.92</v>
+        <v>366870802.98</v>
       </c>
       <c r="AC3" t="n">
-        <v>440116.47</v>
+        <v>-11109156.46</v>
       </c>
       <c r="AD3" t="n">
-        <v>118243273.8</v>
+        <v>118452031.51</v>
       </c>
       <c r="AE3" t="n">
-        <v>2337370.02</v>
+        <v>2769069.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>115905903.78</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-100000</v>
-      </c>
+        <v>115682961.73</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-51563656.21</v>
+        <v>1908062.95</v>
       </c>
       <c r="AI3" t="n">
-        <v>-667768724.47</v>
+        <v>-388869180.67</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-596373230.47</v>
+        <v>-161583645.97</v>
       </c>
       <c r="AK3" t="n">
-        <v>30034256.12</v>
+        <v>3692937.45</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1143698960.2</v>
+        <v>-1272018874.56</v>
       </c>
       <c r="AM3" t="n">
-        <v>-28438600.75</v>
+        <v>-21942510.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>-441420552.3</v>
+        <v>-423851512.63</v>
       </c>
       <c r="AO3" t="n">
-        <v>-673839807.15</v>
+        <v>-826224851.03</v>
       </c>
       <c r="AP3" t="n">
-        <v>517291473.61</v>
+        <v>1106742291.14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>64919388.17</v>
+        <v>28579299.48</v>
       </c>
       <c r="AR3" t="n">
-        <v>452372085.44</v>
+        <v>1078162991.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-180496264.05</v>
+        <v>-674255284.55</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>2600000</v>
+        <v>180000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-18912618.08</v>
+        <v>-77882054.08</v>
       </c>
       <c r="F4" t="n">
+        <v>23097948.95</v>
+      </c>
+      <c r="G4" t="n">
         <v>9796343.220000001</v>
       </c>
-      <c r="G4" t="n">
-        <v>40705776.27</v>
-      </c>
       <c r="H4" t="n">
-        <v>-30909433.05</v>
+        <v>13301605.73</v>
       </c>
       <c r="I4" t="n">
-        <v>13747628</v>
+        <v>174510990.28</v>
       </c>
       <c r="J4" t="n">
-        <v>11147628</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>-5100259.72</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-388750</v>
+      </c>
       <c r="L4" t="n">
-        <v>2600000</v>
+        <v>180000000</v>
       </c>
       <c r="M4" t="n">
-        <v>2600000</v>
+        <v>180000000</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>2600000</v>
+        <v>180000000</v>
       </c>
       <c r="P4" t="n">
-        <v>116926584.92</v>
+        <v>435163845.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>133902000</v>
+        <v>433820500</v>
       </c>
       <c r="R4" t="n">
-        <v>1447902000</v>
+        <v>513820500</v>
       </c>
       <c r="S4" t="n">
-        <v>-1314000000</v>
+        <v>-80000000</v>
       </c>
       <c r="T4" t="n">
-        <v>-16975415.08</v>
+        <v>1343345.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1937203</v>
+        <v>79225400</v>
       </c>
       <c r="V4" t="n">
-        <v>-18912618.08</v>
+        <v>-77882054.08</v>
       </c>
       <c r="W4" t="n">
-        <v>-161583645.97</v>
+        <v>-596373230.47</v>
       </c>
       <c r="X4" t="n">
-        <v>-67144583.77</v>
+        <v>-40113299.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>-76920411.81</v>
+        <v>59153027.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>-201199512.98</v>
+        <v>182225344.21</v>
       </c>
       <c r="AA4" t="n">
-        <v>-155895461.96</v>
+        <v>98826765.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>366870802.98</v>
+        <v>-380318435.92</v>
       </c>
       <c r="AC4" t="n">
-        <v>-11109156.46</v>
+        <v>440116.47</v>
       </c>
       <c r="AD4" t="n">
-        <v>118452031.51</v>
+        <v>118243273.8</v>
       </c>
       <c r="AE4" t="n">
-        <v>2769069.78</v>
+        <v>2337370.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>115682961.73</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+        <v>115905903.78</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-100000</v>
+      </c>
       <c r="AH4" t="n">
-        <v>1908062.95</v>
+        <v>-51563656.21</v>
       </c>
       <c r="AI4" t="n">
-        <v>-388869180.67</v>
+        <v>-667768724.47</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-161583645.97</v>
+        <v>-596373230.47</v>
       </c>
       <c r="AK4" t="n">
-        <v>3692937.45</v>
+        <v>30034256.12</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1272018874.56</v>
+        <v>-1143698960.2</v>
       </c>
       <c r="AM4" t="n">
-        <v>-21942510.9</v>
+        <v>-28438600.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>-423851512.63</v>
+        <v>-441420552.3</v>
       </c>
       <c r="AO4" t="n">
-        <v>-826224851.03</v>
+        <v>-673839807.15</v>
       </c>
       <c r="AP4" t="n">
-        <v>1106742291.14</v>
+        <v>517291473.61</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28579299.48</v>
+        <v>64919388.17</v>
       </c>
       <c r="AR4" t="n">
-        <v>1078162991.66</v>
+        <v>452372085.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>134544640.53</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+        <v>-531618207.94</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-230000000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>769574489.53</v>
+      </c>
       <c r="E5" t="n">
-        <v>-12903370.69</v>
+        <v>-37800931.38</v>
       </c>
       <c r="F5" t="n">
-        <v>40705776.27</v>
+        <v>17505838.28</v>
       </c>
       <c r="G5" t="n">
-        <v>129107915.6</v>
+        <v>23097948.95</v>
       </c>
       <c r="H5" t="n">
-        <v>-88402139.33</v>
+        <v>-5592110.67</v>
       </c>
       <c r="I5" t="n">
-        <v>-42432264.28</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>525590847.27</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-2751428.13</v>
+      </c>
       <c r="K5" t="n">
-        <v>-42432264.28</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>-11232214.13</v>
+      </c>
+      <c r="L5" t="n">
+        <v>539574489.53</v>
+      </c>
+      <c r="M5" t="n">
+        <v>539574489.53</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-230000000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>769574489.53</v>
+      </c>
       <c r="P5" t="n">
-        <v>-193417886.27</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-194764999</v>
-      </c>
-      <c r="R5" t="n">
-        <v>455235001</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-650000000</v>
-      </c>
+        <v>-37365681.38</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>1347112.73</v>
+        <v>-37365681.38</v>
       </c>
       <c r="U5" t="n">
-        <v>14250483.42</v>
+        <v>435250</v>
       </c>
       <c r="V5" t="n">
-        <v>-12903370.69</v>
+        <v>-37800931.38</v>
       </c>
       <c r="W5" t="n">
-        <v>147448011.22</v>
+        <v>-493817276.56</v>
       </c>
       <c r="X5" t="n">
-        <v>4305432.87</v>
+        <v>-270879187.39</v>
       </c>
       <c r="Y5" t="n">
-        <v>1703373.22</v>
+        <v>-8124803.78</v>
       </c>
       <c r="Z5" t="n">
-        <v>-91990611.37</v>
+        <v>-158007027.69</v>
       </c>
       <c r="AA5" t="n">
-        <v>-45074276.8</v>
+        <v>-24898272.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>139666947.82</v>
+        <v>-79849083.87</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9589220.74</v>
+        <v>12119549.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>116876370.6</v>
+        <v>165843613.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>3031318.47</v>
+        <v>4800509.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>113845052.13</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>161043103.68</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-805273.24</v>
+      </c>
       <c r="AH5" t="n">
-        <v>-7474097.45</v>
+        <v>3927706.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>4294957.73</v>
+        <v>-502560250.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>147448011.22</v>
+        <v>-493817276.56</v>
       </c>
       <c r="AK5" t="n">
-        <v>-136545917.81</v>
+        <v>-32319618.93</v>
       </c>
       <c r="AL5" t="n">
-        <v>-981942740.05</v>
+        <v>-1463642099.72</v>
       </c>
       <c r="AM5" t="n">
-        <v>-26366028.62</v>
+        <v>-43235046.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>-351895863.3</v>
+        <v>-457751016.15</v>
       </c>
       <c r="AO5" t="n">
-        <v>-603680848.13</v>
+        <v>-962656037.17</v>
       </c>
       <c r="AP5" t="n">
-        <v>1265936669.08</v>
+        <v>1002144442.09</v>
       </c>
       <c r="AQ5" t="n">
-        <v>28858886.66</v>
+        <v>38342746.31</v>
       </c>
       <c r="AR5" t="n">
-        <v>1237077782.42</v>
+        <v>963801695.78</v>
       </c>
     </row>
   </sheetData>
@@ -3630,182 +3630,182 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EI1" t="inlineStr">
@@ -3907,28 +3907,28 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>7.13</v>
+        <v>6.53</v>
       </c>
       <c r="U2" t="n">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="V2" t="n">
-        <v>6.94</v>
+        <v>6.37</v>
       </c>
       <c r="W2" t="n">
-        <v>7.21</v>
+        <v>6.73</v>
       </c>
       <c r="X2" t="n">
-        <v>7.13</v>
+        <v>6.53</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.94</v>
+        <v>6.37</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.21</v>
+        <v>6.73</v>
       </c>
       <c r="AB2" t="n">
         <v>1624406400</v>
@@ -3937,25 +3937,25 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>5166200</v>
+        <v>8025010</v>
       </c>
       <c r="AE2" t="n">
-        <v>5166200</v>
+        <v>8025010</v>
       </c>
       <c r="AF2" t="n">
-        <v>9081121</v>
+        <v>7569693</v>
       </c>
       <c r="AG2" t="n">
-        <v>6189486</v>
+        <v>10758232</v>
       </c>
       <c r="AH2" t="n">
-        <v>6189486</v>
+        <v>10758232</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.98</v>
+        <v>6.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6.99</v>
+        <v>6.71</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -3964,13 +3964,13 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>2743170048</v>
+        <v>2640695296</v>
       </c>
       <c r="AN2" t="n">
-        <v>2743170016</v>
+        <v>2573692558</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.92</v>
+        <v>6.37</v>
       </c>
       <c r="AP2" t="n">
         <v>10.93</v>
@@ -3982,13 +3982,13 @@
         <v>3.159041</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.6209546</v>
+        <v>1.5445938</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.0792</v>
+        <v>7.6556</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.91385</v>
+        <v>8.784599999999999</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3588121600</v>
+        <v>3001964544</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.35478002</v>
+        <v>-0.32379</v>
       </c>
       <c r="BB2" t="n">
-        <v>236991767</v>
+        <v>238809504</v>
       </c>
       <c r="BC2" t="n">
         <v>394133623</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.52479</v>
+        <v>0.51060003</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.053600002</v>
+        <v>0.07831</v>
       </c>
       <c r="BF2" t="n">
         <v>394133623</v>
@@ -4029,7 +4029,7 @@
         <v>2.798</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.487491</v>
+        <v>2.3945675</v>
       </c>
       <c r="BI2" t="n">
         <v>1767139200</v>
@@ -4041,7 +4041,7 @@
         <v>1774915200</v>
       </c>
       <c r="BL2" t="n">
-        <v>-600395456</v>
+        <v>-553556352</v>
       </c>
       <c r="BM2" t="n">
         <v>-1.68</v>
@@ -4055,16 +4055,16 @@
         <v>1132617600</v>
       </c>
       <c r="BP2" t="n">
-        <v>2.12</v>
+        <v>1.756</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-13.66</v>
+        <v>-13.088</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.17339665</v>
+        <v>-0.24245942</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="BT2" t="n">
         <v>0.14</v>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>6.96</v>
+        <v>6.7</v>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
@@ -4089,55 +4089,55 @@
         <v>94987304</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.243</v>
+        <v>0.241</v>
       </c>
       <c r="CA2" t="n">
-        <v>-262670816</v>
+        <v>-229359360</v>
       </c>
       <c r="CB2" t="n">
         <v>456256672</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.22</v>
+        <v>0.229</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.31</v>
+        <v>0.323</v>
       </c>
       <c r="CE2" t="n">
-        <v>1692317568</v>
+        <v>1709637376</v>
       </c>
       <c r="CF2" t="n">
         <v>41.377</v>
       </c>
       <c r="CG2" t="n">
-        <v>4.658</v>
+        <v>5.003</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.11047</v>
+        <v>-0.102239996</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0.56526</v>
+        <v>-0.47588003</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-327442208</v>
+        <v>-296804512</v>
       </c>
       <c r="CK2" t="n">
-        <v>136224160</v>
+        <v>6130223</v>
       </c>
       <c r="CL2" t="n">
-        <v>-299695904</v>
+        <v>-453500960</v>
       </c>
       <c r="CM2" t="n">
         <v>-0.043</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.19349001</v>
+        <v>-0.17361</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0.15521</v>
+        <v>-0.13416</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.25978002</v>
+        <v>-0.25977</v>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
@@ -4177,136 +4177,136 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CY2" t="b">
+      <c r="CY2" t="n">
+        <v>2.6033628</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>NINGXIA YOUNGLIGHT CHEMICALS CO</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>0.1699996</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>6.37 - 6.73</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>7569693</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.32999992</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.051805325</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>6.37 - 10.93</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-4.2300005</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.38700828</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-24.245941</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1619521140</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>1619521140</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.95560026</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.12482369</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-2.0846004</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.23730169</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DV2" t="b">
         <v>0</v>
       </c>
-      <c r="CZ2" t="n">
-        <v>-1.1191998</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>-0.13852854</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>-1.9538498</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>-0.21919258</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>-2.3842926</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="DH2" t="b">
+      <c r="DW2" t="b">
         <v>0</v>
       </c>
-      <c r="DI2" t="n">
+      <c r="DX2" t="n">
         <v>848453400000</v>
       </c>
-      <c r="DJ2" t="n">
-        <v>-0.17000008</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>6.94 - 7.21</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>9081121</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.03999996</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.005780341</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>6.92 - 10.93</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-3.9700003</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.3632205</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-17.339664</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1619521140</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1619521140</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DX2" t="n">
-        <v>1780038243</v>
-      </c>
-      <c r="DY2" t="inlineStr">
+      <c r="DZ2" t="n">
+        <v>1782111852</v>
+      </c>
+      <c r="EA2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>finmb_11168502</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="EC2" t="n">
+      <c r="EE2" t="n">
         <v>28800000</v>
       </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="EE2" t="b">
+      <c r="EG2" t="b">
         <v>0</v>
       </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>NINGXIA YOUNGLIGHT CHEMICALS CO</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>Ningxia Yinglite Chemicals Co., Ltd</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr"/>
